--- a/artfynd/A 4105-2025 artfynd.xlsx
+++ b/artfynd/A 4105-2025 artfynd.xlsx
@@ -820,7 +820,7 @@
         <v>118775447</v>
       </c>
       <c r="B3" t="n">
-        <v>97858</v>
+        <v>98347</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -942,7 +942,11 @@
           <t>Tom Sävström</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">

--- a/artfynd/A 4105-2025 artfynd.xlsx
+++ b/artfynd/A 4105-2025 artfynd.xlsx
@@ -820,7 +820,7 @@
         <v>118775447</v>
       </c>
       <c r="B3" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 4105-2025 artfynd.xlsx
+++ b/artfynd/A 4105-2025 artfynd.xlsx
@@ -820,7 +820,7 @@
         <v>118775447</v>
       </c>
       <c r="B3" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 4105-2025 artfynd.xlsx
+++ b/artfynd/A 4105-2025 artfynd.xlsx
@@ -820,7 +820,7 @@
         <v>118775447</v>
       </c>
       <c r="B3" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 4105-2025 artfynd.xlsx
+++ b/artfynd/A 4105-2025 artfynd.xlsx
@@ -820,7 +820,7 @@
         <v>118775447</v>
       </c>
       <c r="B3" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 4105-2025 artfynd.xlsx
+++ b/artfynd/A 4105-2025 artfynd.xlsx
@@ -820,7 +820,7 @@
         <v>118775447</v>
       </c>
       <c r="B3" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 4105-2025 artfynd.xlsx
+++ b/artfynd/A 4105-2025 artfynd.xlsx
@@ -820,7 +820,7 @@
         <v>118775447</v>
       </c>
       <c r="B3" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 4105-2025 artfynd.xlsx
+++ b/artfynd/A 4105-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1176,6 +1176,125 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129336860</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98678</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Vägkorset gamla/nya väg 233, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>564600</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6626448</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Äldre blandskog, gran, tall, björk</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4105-2025 artfynd.xlsx
+++ b/artfynd/A 4105-2025 artfynd.xlsx
@@ -1181,7 +1181,7 @@
         <v>129336860</v>
       </c>
       <c r="B6" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 4105-2025 artfynd.xlsx
+++ b/artfynd/A 4105-2025 artfynd.xlsx
@@ -1181,7 +1181,7 @@
         <v>129336860</v>
       </c>
       <c r="B6" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 4105-2025 artfynd.xlsx
+++ b/artfynd/A 4105-2025 artfynd.xlsx
@@ -1181,7 +1181,7 @@
         <v>129336860</v>
       </c>
       <c r="B6" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 4105-2025 artfynd.xlsx
+++ b/artfynd/A 4105-2025 artfynd.xlsx
@@ -1181,7 +1181,7 @@
         <v>129336860</v>
       </c>
       <c r="B6" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 4105-2025 artfynd.xlsx
+++ b/artfynd/A 4105-2025 artfynd.xlsx
@@ -1181,7 +1181,7 @@
         <v>129336860</v>
       </c>
       <c r="B6" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 4105-2025 artfynd.xlsx
+++ b/artfynd/A 4105-2025 artfynd.xlsx
@@ -1181,7 +1181,7 @@
         <v>129336860</v>
       </c>
       <c r="B6" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 4105-2025 artfynd.xlsx
+++ b/artfynd/A 4105-2025 artfynd.xlsx
@@ -1181,7 +1181,7 @@
         <v>129336860</v>
       </c>
       <c r="B6" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 4105-2025 artfynd.xlsx
+++ b/artfynd/A 4105-2025 artfynd.xlsx
@@ -1181,7 +1181,7 @@
         <v>129336860</v>
       </c>
       <c r="B6" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 4105-2025 artfynd.xlsx
+++ b/artfynd/A 4105-2025 artfynd.xlsx
@@ -1181,7 +1181,7 @@
         <v>129336860</v>
       </c>
       <c r="B6" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 4105-2025 artfynd.xlsx
+++ b/artfynd/A 4105-2025 artfynd.xlsx
@@ -1181,7 +1181,7 @@
         <v>129336860</v>
       </c>
       <c r="B6" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 4105-2025 artfynd.xlsx
+++ b/artfynd/A 4105-2025 artfynd.xlsx
@@ -1181,7 +1181,7 @@
         <v>129336860</v>
       </c>
       <c r="B6" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 4105-2025 artfynd.xlsx
+++ b/artfynd/A 4105-2025 artfynd.xlsx
@@ -1181,7 +1181,7 @@
         <v>129336860</v>
       </c>
       <c r="B6" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
